--- a/outputs/evaluation/decision/v1/CF_M08/run_3/CF_M08_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M08/run_3/CF_M08_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,71 +471,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CF_M08_AD01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CF_M08_C08, *CF_M08_C09</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CF_M08_AU03</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Access Requirement; Availability</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Traefik</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Funciona como un proxy inverso y balanceador de carga. • Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service). • Expone los puertos 80 (HTTP) y 443 (HTTPS) al mundo exterior y redirige el tráfico a los servicios internos según las reglas definidas.</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7311</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>CF_M08_AD02</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
 directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>*CF_M08_C10</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>CF_M08_AU03</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>43</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Responsiveness</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Traefik</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Traefik acts as a reverse proxy and load balancer, managing HTTP and HTTPS request routing, improving availability and responsiveness.</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.7841</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CF_M08_AD03</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>*CF_M08_C11, *CF_M08_C12</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -543,90 +543,90 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Security; Integrity</t>
+          <t>Responsiveness</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Traefik acts as a reverse proxy and load balancer, managing HTTP and HTTPS request routing, improving availability and responsiveness.</t>
+          <t>Funciona como un proxy inverso y balanceador de carga. • Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service). • Expone los puertos 80 (HTTP) y 443 (HTTPS) al mundo exterior y redirige el tráfico a los servicios internos según las reglas definidas.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.6564</v>
+        <v>0.7491</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_AD04</t>
+          <t>CF_M08_AD03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This facilitates the creation of paths by simply adding files and folders inside the src directory.</t>
+          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M08_C14</t>
+          <t>*CF_M08_C11, *CF_M08_C12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ease</t>
+          <t>Security; Integrity</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AD_08</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Docker is a containerization platform used to manage the execution of the application services, allowing to create an application and package it together with its dependencies and libraries.</t>
+          <t>Funciona como un proxy inverso y balanceador de carga. • Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service). • Expone los puertos 80 (HTTP) y 443 (HTTPS) al mundo exterior y redirige el tráfico a los servicios internos según las reglas definidas.</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.576</v>
+        <v>0.6475</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M08_AD06</t>
+          <t>CF_M08_AD04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>It includes automatic optimizations for images, fonts and scripts, improving the performance of the application.</t>
+          <t>This facilitates the creation of paths by simply adding files and folders inside the src directory.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>*CF_M08_C16</t>
+          <t>*CF_M08_C14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Ease</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -649,32 +649,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that supports both client-side and server-side rendering, allowing to choose the best strategy according to the needs of the application.</t>
+          <t>El patrón Component-Based se centra en la construcción de la interfaz de usuario mediante la creación de componentes independientes y reutilizables. Cada componente encapsula su propia lógica, estilos y estructura, lo que permite que estos se desarrollen, mantengan y prueben de manera aislada.</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.6673</v>
+        <v>0.5717</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
+          <t>Next.js supports several styling methods, including CSS, Tailwind CSS and CSS-in-JS modules, offering flexibility in style management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>*CF_M08_C17</t>
+          <t>*CF_M08_C15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -683,11 +683,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Stylization</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -697,176 +697,176 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that supports both client-side and server-side rendering, allowing to choose the best strategy according to the needs of the application.</t>
+          <t>Funciona como un proxy inverso y balanceador de carga. • Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service). • Expone los puertos 80 (HTTP) y 443 (HTTPS) al mundo exterior y redirige el tráfico a los servicios internos según las reglas definidas.</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.697</v>
+        <v>0.6253</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M08_AD08</t>
+          <t>CF_M08_AD06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
+          <t>It includes automatic optimizations for images, fonts and scripts, improving the performance of the application.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>*CF_M08_C18, *CF_M08_C19</t>
+          <t>*CF_M08_C16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Efficiency (of development); Flexibility</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components, promoting modularity, code reuse, and maintainability.</t>
+          <t>Sirve la aplicación web mediante React.</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.6963</v>
+        <v>0.6293</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M08_AD09</t>
+          <t>CF_M08_AD07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
+          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>*CF_M08_C20, *CF_M08_C21</t>
+          <t>*CF_M08_C17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Reuse; Modularity</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Next.js</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components, promoting modularity, code reuse, and maintainability.</t>
+          <t>El patrón Component-Based se centra en la construcción de la interfaz de usuario mediante la creación de componentes independientes y reutilizables. Cada componente encapsula su propia lógica, estilos y estructura, lo que permite que estos se desarrollen, mantengan y prueben de manera aislada.</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.7297</v>
+        <v>0.6933</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M08_AD10</t>
+          <t>CF_M08_AD08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>It is designed to simplify access and database management</t>
+          <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>*CF_M08_C22</t>
+          <t>*CF_M08_C18, *CF_M08_C19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Simplification (of development)</t>
+          <t>Efficiency; Flexibility</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prisma</t>
+          <t>React</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Prisma is an ORM tool used to simplify database access and management.</t>
+          <t>Sirve la aplicación web mediante React.</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.7812</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M08_AD11</t>
+          <t>CF_M08_AD10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
+          <t>It is designed to simplify access and database management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>*CF_M08_C23</t>
+          <t>*CF_M08_C22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Compatibility</t>
+          <t>Simplification (of development)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -889,16 +889,112 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Prisma is an ORM tool used to simplify database access and management.</t>
+          <t>Proporciona la base de datos relacional para almacenar los datos de la aplicación. • Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.7723</v>
+        <v>0.7136</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CF_M08_AD12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>*CF_M08_C24</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CF_M08_AU09</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Depuration</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Prisma</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Proporciona la base de datos relacional para almacenar los datos de la aplicación. • Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7378</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M08_AD14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>*CF_M08_C21, CF_M08_C05</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CF_M08_P03</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>66</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Modularity; Maintenance Requirements</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Component-based</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>El patrón Component-Based se centra en la construcción de la interfaz de usuario mediante la creación de componentes independientes y reutilizables. Cada componente encapsula su propia lógica, estilos y estructura, lo que permite que estos se desarrollen, mantengan y prueben de manera aislada.</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7347</v>
       </c>
     </row>
   </sheetData>
